--- a/capstone/sprint1/26-09-sprint-1-initial-metrics.xlsx
+++ b/capstone/sprint1/26-09-sprint-1-initial-metrics.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Lewis\Software\Stone-Ocean-Backlogs\capstone\sprint1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68D513B8-7E53-4DD7-9C0C-0A041BB13974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ABDBBB4-5CC2-4EA3-8F62-BC814569E75A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Example" sheetId="8" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="44">
   <si>
     <t>Name</t>
   </si>
@@ -170,6 +170,9 @@
   </si>
   <si>
     <t>August 29th, 1:26pm</t>
+  </si>
+  <si>
+    <t>September 6th, 1:00pm</t>
   </si>
 </sst>
 </file>
@@ -37137,23 +37140,23 @@
         <v>9</v>
       </c>
       <c r="D9" s="7">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E9" s="7">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F9" s="8"/>
       <c r="G9" s="9">
         <f t="shared" ref="G9:H12" si="0">D9/B9</f>
-        <v>0</v>
+        <v>0.875</v>
       </c>
       <c r="H9" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="I9" s="10">
         <f t="shared" ref="I9:I16" si="1">E9/B9</f>
-        <v>0</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15.75" customHeight="1">
@@ -37167,23 +37170,23 @@
         <v>8</v>
       </c>
       <c r="D10" s="7">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E10" s="7">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F10" s="8"/>
       <c r="G10" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.625</v>
       </c>
       <c r="H10" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15.75" customHeight="1">
@@ -37197,23 +37200,23 @@
         <v>8</v>
       </c>
       <c r="D11" s="7">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="E11" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F11" s="8"/>
       <c r="G11" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.8125</v>
       </c>
       <c r="H11" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="I11" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15.75" customHeight="1">
@@ -37227,23 +37230,23 @@
         <v>11</v>
       </c>
       <c r="D12" s="7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E12" s="7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F12" s="8"/>
       <c r="G12" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="H12" s="10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.36363636363636365</v>
       </c>
       <c r="I12" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="15.75" customHeight="1">
@@ -37293,24 +37296,24 @@
       </c>
       <c r="D16" s="7">
         <f>SUM(D9:D14)</f>
-        <v>0</v>
+        <v>31.5</v>
       </c>
       <c r="E16" s="7">
         <f>SUM(E9:E14)</f>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F16" s="8"/>
       <c r="G16" s="9">
         <f t="shared" ref="G16:H16" si="2">D16/B16</f>
-        <v>0</v>
+        <v>0.984375</v>
       </c>
       <c r="H16" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.61111111111111116</v>
       </c>
       <c r="I16" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.6875</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="15.75" customHeight="1">
@@ -37387,9 +37390,13 @@
       <c r="A24" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B24" s="16"/>
+      <c r="B24" s="16" t="s">
+        <v>41</v>
+      </c>
       <c r="C24" s="16"/>
-      <c r="D24" s="17"/>
+      <c r="D24" s="17" t="s">
+        <v>43</v>
+      </c>
       <c r="E24" s="3"/>
     </row>
     <row r="25" spans="1:9" ht="15.75" customHeight="1">

--- a/capstone/sprint1/26-09-sprint-1-initial-metrics.xlsx
+++ b/capstone/sprint1/26-09-sprint-1-initial-metrics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Lewis\Software\Stone-Ocean-Backlogs\capstone\sprint1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ABDBBB4-5CC2-4EA3-8F62-BC814569E75A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51546A50-70FB-4D13-BDB6-53EDFFFE46EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37140,7 +37140,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E9" s="7">
         <v>7</v>
@@ -37148,7 +37148,7 @@
       <c r="F9" s="8"/>
       <c r="G9" s="9">
         <f t="shared" ref="G9:H12" si="0">D9/B9</f>
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="H9" s="10">
         <f t="shared" si="0"/>
@@ -37296,7 +37296,7 @@
       </c>
       <c r="D16" s="7">
         <f>SUM(D9:D14)</f>
-        <v>31.5</v>
+        <v>32.5</v>
       </c>
       <c r="E16" s="7">
         <f>SUM(E9:E14)</f>
@@ -37305,7 +37305,7 @@
       <c r="F16" s="8"/>
       <c r="G16" s="9">
         <f t="shared" ref="G16:H16" si="2">D16/B16</f>
-        <v>0.984375</v>
+        <v>1.015625</v>
       </c>
       <c r="H16" s="10">
         <f t="shared" si="2"/>
